--- a/backend/data_wizard/import_templates/risk_assessment_template.xlsx
+++ b/backend/data_wizard/import_templates/risk_assessment_template.xlsx
@@ -1,196 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohamedhacene/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532200C7-572B-E94F-9621-25545F44F642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19980" xr2:uid="{1E3282CF-9D23-8B44-A0A5-0B7E449DE1FE}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
-  <si>
-    <t>ref_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>existing_controls</t>
-  </si>
-  <si>
-    <t>inherent_impact</t>
-  </si>
-  <si>
-    <t>inherent_proba</t>
-  </si>
-  <si>
-    <t>inherent_level</t>
-  </si>
-  <si>
-    <t>current_impact</t>
-  </si>
-  <si>
-    <t>current_proba</t>
-  </si>
-  <si>
-    <t>current_level</t>
-  </si>
-  <si>
-    <t>additional_controls</t>
-  </si>
-  <si>
-    <t>residual_impact</t>
-  </si>
-  <si>
-    <t>residual_proba</t>
-  </si>
-  <si>
-    <t>residual_level</t>
-  </si>
-  <si>
-    <t>R01</t>
-  </si>
-  <si>
-    <t>R02</t>
-  </si>
-  <si>
-    <t>R03</t>
-  </si>
-  <si>
-    <t>this</t>
-  </si>
-  <si>
-    <t>can</t>
-  </si>
-  <si>
-    <t>be</t>
-  </si>
-  <si>
-    <t>bad</t>
-  </si>
-  <si>
-    <t>R04</t>
-  </si>
-  <si>
-    <t>mineur</t>
-  </si>
-  <si>
-    <t>important</t>
-  </si>
-  <si>
-    <t>significatif</t>
-  </si>
-  <si>
-    <t>critique</t>
-  </si>
-  <si>
-    <t>vraisemblable</t>
-  </si>
-  <si>
-    <t>alpha
-omega</t>
-  </si>
-  <si>
-    <t>omega</t>
-  </si>
-  <si>
-    <t>beta</t>
-  </si>
-  <si>
-    <t>alpha
-beta
-gamma</t>
-  </si>
-  <si>
-    <t>unlikely</t>
-  </si>
-  <si>
-    <t>very likely</t>
-  </si>
-  <si>
-    <t>certain</t>
-  </si>
-  <si>
-    <t>treatment</t>
-  </si>
-  <si>
-    <t>mitigate</t>
-  </si>
-  <si>
-    <t>transfer</t>
-  </si>
-  <si>
-    <t>avoid</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -209,26 +66,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -548,189 +464,319 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35B75F0-636B-7A44-9A19-B785E175983B}">
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5" bestFit="1" customWidth="1"/>
+    <col width="13.5" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="13.5" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="14.5" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="17.1640625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="13.1640625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="13.6640625" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="12.5" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>34</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ref_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>inherent_proba</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>inherent_impact</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inherent_level</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>existing_controls</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>current_proba</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>current_impact</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>current_level</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>additional_controls</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>residual_proba</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>residual_impact</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>residual_level</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>37</v>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>this</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>vraisemblable</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mineur</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>alpha
+omega</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vraisemblable</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>mineur</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>vraisemblable</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>mineur</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>avoid</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>erp
+database server</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>omega</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>important</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>erp</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>35</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>be</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>very likely</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>significatif</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>very likely</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>significatif</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>mitigate</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" t="s">
-        <v>36</v>
+    <row r="5" ht="51" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>critique</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>certain</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>critique</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>alpha
+beta
+gamma</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>customer portal</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>